--- a/BladesItems.xlsx
+++ b/BladesItems.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9605B7-D4B9-4073-B5A2-7C6CA6D0A6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9E35A2-CB22-4843-9A31-E0E9CBBB8319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="4" xr2:uid="{06410ABF-0E56-4863-8318-F9923E5A9ABB}"/>
+    <workbookView xWindow="11295" yWindow="345" windowWidth="14730" windowHeight="15570" activeTab="5" xr2:uid="{06410ABF-0E56-4863-8318-F9923E5A9ABB}"/>
   </bookViews>
   <sheets>
     <sheet name="All Items" sheetId="1" r:id="rId1"/>
@@ -13,8 +13,10 @@
     <sheet name="Armor" sheetId="3" r:id="rId3"/>
     <sheet name="Weapons" sheetId="5" r:id="rId4"/>
     <sheet name="Blades Effects" sheetId="4" r:id="rId5"/>
+    <sheet name="Costs" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2950" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2952" uniqueCount="755">
   <si>
     <t>Name</t>
   </si>
@@ -2319,6 +2321,12 @@
   </si>
   <si>
     <t>Skyrim Effects</t>
+  </si>
+  <si>
+    <t>Prices</t>
+  </si>
+  <si>
+    <t>Item Costs</t>
   </si>
 </sst>
 </file>
@@ -2370,7 +2378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -2393,15 +2401,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11236,7 +11243,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03CA207-6AE7-4003-87BF-0F522E63B18E}">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -11986,117 +11993,6 @@
       </c>
       <c r="L21" t="s">
         <v>516</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="str" cm="1">
-        <f t="array" ref="A23:F23">TRANSPOSE(_xlfn._xlws.SORT(_xlfn.UNIQUE(E2:E21)))</f>
-        <v>333Sigils</v>
-      </c>
-      <c r="B23" t="str">
-        <v>444Sigils</v>
-      </c>
-      <c r="C23" t="str">
-        <v>499Sigils</v>
-      </c>
-      <c r="D23" t="str">
-        <v>555Sigils</v>
-      </c>
-      <c r="E23" t="str">
-        <v>777Sigils</v>
-      </c>
-      <c r="F23" t="str">
-        <v>899Sigils</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="str" cm="1">
-        <f t="array" ref="A24:A25">_xlfn._xlws.FILTER($A$2:$A$21,$E$2:$E$21=A23)</f>
-        <v>Flame Monarch's Crown</v>
-      </c>
-      <c r="B24" t="str" cm="1">
-        <f t="array" ref="B24">_xlfn._xlws.FILTER($A$2:$A$21,$E$2:$E$21=B23)</f>
-        <v>Conjurer's Gloves</v>
-      </c>
-      <c r="C24" t="str" cm="1">
-        <f t="array" ref="C24">_xlfn._xlws.FILTER($A$2:$A$21,$E$2:$E$21=C23)</f>
-        <v>Boots of Dispersion</v>
-      </c>
-      <c r="D24" t="str" cm="1">
-        <f t="array" ref="D24:D26">_xlfn._xlws.FILTER($A$2:$A$21,$E$2:$E$21=D23)</f>
-        <v>Areldur's Armor</v>
-      </c>
-      <c r="E24" t="str" cm="1">
-        <f t="array" ref="E24">_xlfn._xlws.FILTER($A$2:$A$21,$E$2:$E$21=E23)</f>
-        <v>Shield of Stasis</v>
-      </c>
-      <c r="F24" t="str" cm="1">
-        <f t="array" ref="F24:F35">_xlfn._xlws.FILTER($A$2:$A$21,$E$2:$E$21=F23)</f>
-        <v>Baridan's Axe</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="str">
-        <v>Paladin's Helmet</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Paladin's Mail</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Breathtaker</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="D26" t="str">
-        <v>Purifier's Cocoon</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Captain Kordan's Saber</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="F27" t="str">
-        <v>Lichslayer</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="F28" t="str">
-        <v>Maul of the Aureal</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="F29" t="str">
-        <v>Mephala's Teacher</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="F30" t="str">
-        <v>Serpentstrike</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="F31" t="str">
-        <v>Spiderfang</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="F32" t="str">
-        <v>Stormkiss</v>
-      </c>
-    </row>
-    <row r="33" spans="6:6">
-      <c r="F33" t="str">
-        <v>Sunderblade</v>
-      </c>
-    </row>
-    <row r="34" spans="6:6">
-      <c r="F34" t="str">
-        <v>Thunderfell</v>
-      </c>
-    </row>
-    <row r="35" spans="6:6">
-      <c r="F35" t="str">
-        <v>Witsplinter</v>
       </c>
     </row>
   </sheetData>
@@ -12128,49 +12024,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>538</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>577</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>692</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="15" t="s">
         <v>576</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16" t="s">
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16" t="s">
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
       <c r="I2" t="s">
         <v>750</v>
       </c>
@@ -12189,7 +12085,7 @@
       <c r="N2" t="s">
         <v>700</v>
       </c>
-      <c r="O2" s="16"/>
+      <c r="O2" s="14"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="10" t="s">
@@ -13436,49 +13332,49 @@
     <col min="10" max="10" width="36.375" style="4" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="4" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.25" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="80.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>538</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>611</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="18" t="s">
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="17" t="s">
         <v>671</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="16" t="s">
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
       <c r="G2" t="s">
         <v>750</v>
       </c>
@@ -13503,13 +13399,13 @@
       <c r="N2" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="O2" s="16"/>
+      <c r="O2" s="14"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="16" t="s">
         <v>460</v>
       </c>
       <c r="C3" s="10"/>
@@ -13541,10 +13437,10 @@
       <c r="L3" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3">
         <v>20</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3">
         <v>1</v>
       </c>
       <c r="O3" s="11" t="s">
@@ -13553,7 +13449,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="10"/>
-      <c r="B4" s="14"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="13"/>
@@ -13573,17 +13469,17 @@
       <c r="L4" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4">
         <v>50</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4">
         <v>6</v>
       </c>
       <c r="O4" s="11"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="10"/>
-      <c r="B5" s="14"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="13"/>
@@ -13606,10 +13502,10 @@
       <c r="L5" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5">
         <v>20</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5">
         <v>20</v>
       </c>
       <c r="O5" s="11"/>
@@ -13650,10 +13546,10 @@
       <c r="L6" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6">
         <v>15</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6">
         <v>1</v>
       </c>
       <c r="O6" s="11" t="s">
@@ -13685,10 +13581,10 @@
       <c r="L7" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7">
         <v>20</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7">
         <v>20</v>
       </c>
       <c r="O7" s="11"/>
@@ -13718,10 +13614,10 @@
       <c r="L8" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8">
         <v>20</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8">
         <v>20</v>
       </c>
       <c r="O8" s="11"/>
@@ -13730,7 +13626,7 @@
       <c r="A9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="16" t="s">
         <v>541</v>
       </c>
       <c r="C9" s="10"/>
@@ -13762,10 +13658,10 @@
       <c r="L9" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9">
         <v>15</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9">
         <v>1</v>
       </c>
       <c r="O9" s="11" t="s">
@@ -13774,7 +13670,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="10"/>
-      <c r="B10" s="14"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="E10" s="13"/>
@@ -13797,17 +13693,17 @@
       <c r="L10" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10">
         <v>20</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10">
         <v>20</v>
       </c>
       <c r="O10" s="11"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="10"/>
-      <c r="B11" s="14"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="13"/>
@@ -13830,10 +13726,10 @@
       <c r="L11" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11">
         <v>20</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11">
         <v>20</v>
       </c>
       <c r="O11" s="11"/>
@@ -13874,10 +13770,10 @@
       <c r="L12" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12">
         <v>20</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12">
         <v>1</v>
       </c>
       <c r="O12" s="11" t="s">
@@ -13906,10 +13802,10 @@
       <c r="L13" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13">
         <v>1</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13">
         <v>10</v>
       </c>
       <c r="O13" s="11"/>
@@ -13939,10 +13835,10 @@
       <c r="L14" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14">
         <v>20</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14">
         <v>20</v>
       </c>
       <c r="O14" s="11"/>
@@ -13983,10 +13879,10 @@
       <c r="L15" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15">
         <v>20</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15">
         <v>1</v>
       </c>
       <c r="O15" s="11" t="s">
@@ -14015,10 +13911,10 @@
       <c r="L16" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16">
         <v>1</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16">
         <v>10</v>
       </c>
       <c r="O16" s="11"/>
@@ -14048,10 +13944,10 @@
       <c r="L17" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M17" s="15">
+      <c r="M17">
         <v>20</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17">
         <v>20</v>
       </c>
       <c r="O17" s="11"/>
@@ -14060,7 +13956,7 @@
       <c r="A18" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="16" t="s">
         <v>541</v>
       </c>
       <c r="C18" s="10"/>
@@ -14092,10 +13988,10 @@
       <c r="L18" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="M18" s="15">
+      <c r="M18">
         <v>20</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18">
         <v>1</v>
       </c>
       <c r="O18" s="11" t="s">
@@ -14104,7 +14000,7 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="10"/>
-      <c r="B19" s="14"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="13"/>
@@ -14124,17 +14020,17 @@
       <c r="L19" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19">
         <v>50</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19">
         <v>6</v>
       </c>
       <c r="O19" s="11"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="10"/>
-      <c r="B20" s="14"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="13"/>
@@ -14157,10 +14053,10 @@
       <c r="L20" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20">
         <v>20</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20">
         <v>20</v>
       </c>
       <c r="O20" s="11"/>
@@ -14201,10 +14097,10 @@
       <c r="L21" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21">
         <v>25</v>
       </c>
-      <c r="N21" s="15">
+      <c r="N21">
         <v>1</v>
       </c>
       <c r="O21" s="11" t="s">
@@ -14236,10 +14132,10 @@
       <c r="L22" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M22" s="15">
+      <c r="M22">
         <v>20</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22">
         <v>20</v>
       </c>
       <c r="O22" s="11"/>
@@ -14269,10 +14165,10 @@
       <c r="L23" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M23" s="15">
+      <c r="M23">
         <v>20</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23">
         <v>20</v>
       </c>
       <c r="O23" s="11"/>
@@ -14313,10 +14209,10 @@
       <c r="L24" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="M24" s="15">
+      <c r="M24">
         <v>25</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24">
         <v>1</v>
       </c>
       <c r="O24" s="11" t="s">
@@ -14348,10 +14244,10 @@
       <c r="L25" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M25" s="15">
+      <c r="M25">
         <v>20</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25">
         <v>20</v>
       </c>
       <c r="O25" s="11"/>
@@ -14381,10 +14277,10 @@
       <c r="L26" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M26" s="15">
+      <c r="M26">
         <v>20</v>
       </c>
-      <c r="N26" s="15">
+      <c r="N26">
         <v>20</v>
       </c>
       <c r="O26" s="11"/>
@@ -14393,7 +14289,7 @@
       <c r="A27" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="16" t="s">
         <v>541</v>
       </c>
       <c r="C27" s="10"/>
@@ -14425,10 +14321,10 @@
       <c r="L27" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="M27" s="15">
+      <c r="M27">
         <v>20</v>
       </c>
-      <c r="N27" s="15">
+      <c r="N27">
         <v>1</v>
       </c>
       <c r="O27" s="11" t="s">
@@ -14437,7 +14333,7 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="10"/>
-      <c r="B28" s="14"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
       <c r="E28" s="13"/>
@@ -14457,17 +14353,17 @@
       <c r="L28" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="M28" s="15">
+      <c r="M28">
         <v>50</v>
       </c>
-      <c r="N28" s="15">
+      <c r="N28">
         <v>6</v>
       </c>
       <c r="O28" s="11"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="10"/>
-      <c r="B29" s="14"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
       <c r="E29" s="13"/>
@@ -14490,10 +14386,10 @@
       <c r="L29" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M29" s="15">
+      <c r="M29">
         <v>20</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29">
         <v>20</v>
       </c>
       <c r="O29" s="11"/>
@@ -14502,7 +14398,7 @@
       <c r="A30" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="16" t="s">
         <v>541</v>
       </c>
       <c r="C30" s="10"/>
@@ -14534,10 +14430,10 @@
       <c r="L30" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="M30" s="15">
+      <c r="M30">
         <v>30</v>
       </c>
-      <c r="N30" s="15">
+      <c r="N30">
         <v>1</v>
       </c>
       <c r="O30" s="11" t="s">
@@ -14546,7 +14442,7 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="10"/>
-      <c r="B31" s="14"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
       <c r="E31" s="13"/>
@@ -14569,17 +14465,17 @@
       <c r="L31" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M31" s="15">
+      <c r="M31">
         <v>20</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31">
         <v>20</v>
       </c>
       <c r="O31" s="11"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="10"/>
-      <c r="B32" s="14"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="13"/>
@@ -14634,10 +14530,10 @@
       <c r="L33" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="M33" s="15">
+      <c r="M33">
         <v>15</v>
       </c>
-      <c r="N33" s="15">
+      <c r="N33">
         <v>1</v>
       </c>
       <c r="O33" s="11" t="s">
@@ -14669,10 +14565,10 @@
       <c r="L34" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M34" s="15">
+      <c r="M34">
         <v>20</v>
       </c>
-      <c r="N34" s="15">
+      <c r="N34">
         <v>20</v>
       </c>
       <c r="O34" s="11"/>
@@ -14702,10 +14598,10 @@
       <c r="L35" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M35" s="15">
+      <c r="M35">
         <v>20</v>
       </c>
-      <c r="N35" s="15">
+      <c r="N35">
         <v>20</v>
       </c>
       <c r="O35" s="11"/>
@@ -14714,7 +14610,7 @@
       <c r="A36" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="16" t="s">
         <v>541</v>
       </c>
       <c r="C36" s="10"/>
@@ -14746,10 +14642,10 @@
       <c r="L36" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="M36" s="15">
+      <c r="M36">
         <v>30</v>
       </c>
-      <c r="N36" s="15">
+      <c r="N36">
         <v>1</v>
       </c>
       <c r="O36" s="11" t="s">
@@ -14758,7 +14654,7 @@
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="10"/>
-      <c r="B37" s="14"/>
+      <c r="B37" s="16"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
       <c r="E37" s="13"/>
@@ -14781,17 +14677,17 @@
       <c r="L37" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M37" s="15">
+      <c r="M37">
         <v>20</v>
       </c>
-      <c r="N37" s="15">
+      <c r="N37">
         <v>20</v>
       </c>
       <c r="O37" s="11"/>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="10"/>
-      <c r="B38" s="14"/>
+      <c r="B38" s="16"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="13"/>
@@ -14814,10 +14710,10 @@
       <c r="L38" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="M38" s="15">
+      <c r="M38">
         <v>20</v>
       </c>
-      <c r="N38" s="15">
+      <c r="N38">
         <v>20</v>
       </c>
       <c r="O38" s="11"/>
@@ -15422,4 +15318,168 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BA82358-C791-43FE-B817-7257A2651CF2}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>754</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" cm="1">
+        <f t="array" ref="A2:A7">_xlfn._xlws.SORT(_xlfn.NUMBERVALUE(_xlfn.TEXTBEFORE(_xlfn.UNIQUE(_xlfn.TAKE(_xlfn.TRIMRANGE('Artifacts Only'!E:E),1-ROWS(_xlfn.TRIMRANGE('Artifacts Only'!E:E)))),"Sigils")))</f>
+        <v>333</v>
+      </c>
+      <c r="C2" cm="1">
+        <f t="array" ref="C2:H2">TRANSPOSE(_xlfn.ANCHORARRAY(A2))</f>
+        <v>333</v>
+      </c>
+      <c r="D2">
+        <v>444</v>
+      </c>
+      <c r="E2">
+        <v>499</v>
+      </c>
+      <c r="F2">
+        <v>555</v>
+      </c>
+      <c r="G2">
+        <v>777</v>
+      </c>
+      <c r="H2">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>444</v>
+      </c>
+      <c r="C3" t="str" cm="1">
+        <f t="array" ref="C3:C4">_xlfn._xlws.FILTER('Artifacts Only'!$A$2:$A$21,'Artifacts Only'!$E$2:$E$21=Costs!C2&amp;"Sigils")</f>
+        <v>Flame Monarch's Crown</v>
+      </c>
+      <c r="D3" t="str" cm="1">
+        <f t="array" ref="D3">_xlfn._xlws.FILTER('Artifacts Only'!$A$2:$A$21,'Artifacts Only'!$E$2:$E$21=Costs!D2&amp;"Sigils")</f>
+        <v>Conjurer's Gloves</v>
+      </c>
+      <c r="E3" t="str" cm="1">
+        <f t="array" ref="E3">_xlfn._xlws.FILTER('Artifacts Only'!$A$2:$A$21,'Artifacts Only'!$E$2:$E$21=Costs!E2&amp;"Sigils")</f>
+        <v>Boots of Dispersion</v>
+      </c>
+      <c r="F3" t="str" cm="1">
+        <f t="array" ref="F3:F5">_xlfn._xlws.FILTER('Artifacts Only'!$A$2:$A$21,'Artifacts Only'!$E$2:$E$21=Costs!F2&amp;"Sigils")</f>
+        <v>Areldur's Armor</v>
+      </c>
+      <c r="G3" t="str" cm="1">
+        <f t="array" ref="G3">_xlfn._xlws.FILTER('Artifacts Only'!$A$2:$A$21,'Artifacts Only'!$E$2:$E$21=Costs!G2&amp;"Sigils")</f>
+        <v>Shield of Stasis</v>
+      </c>
+      <c r="H3" t="str" cm="1">
+        <f t="array" ref="H3:H14">_xlfn._xlws.FILTER('Artifacts Only'!$A$2:$A$21,'Artifacts Only'!$E$2:$E$21=Costs!H2&amp;"Sigils")</f>
+        <v>Baridan's Axe</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>499</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Paladin's Helmet</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Paladin's Mail</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Breathtaker</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>555</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Purifier's Cocoon</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Captain Kordan's Saber</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>777</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Lichslayer</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>899</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Maul of the Aureal</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="H8" t="str">
+        <v>Mephala's Teacher</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="H9" t="str">
+        <v>Serpentstrike</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="H10" t="str">
+        <v>Spiderfang</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="H11" t="str">
+        <v>Stormkiss</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="H12" t="str">
+        <v>Sunderblade</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="H13" t="str">
+        <v>Thunderfell</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="H14" t="str">
+        <v>Witsplinter</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BladesItems.xlsx
+++ b/BladesItems.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9E35A2-CB22-4843-9A31-E0E9CBBB8319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0C4CE8-F7BD-43D8-8B39-89AF1BF84C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11295" yWindow="345" windowWidth="14730" windowHeight="15570" activeTab="5" xr2:uid="{06410ABF-0E56-4863-8318-F9923E5A9ABB}"/>
+    <workbookView xWindow="975" yWindow="0" windowWidth="13905" windowHeight="16200" activeTab="1" xr2:uid="{06410ABF-0E56-4863-8318-F9923E5A9ABB}"/>
   </bookViews>
   <sheets>
     <sheet name="All Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,6 @@
     <sheet name="Costs" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2390,28 +2389,28 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11247,9 +11246,9 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.375" customWidth="1"/>
-    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="13.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.25" customWidth="1"/>
@@ -12024,49 +12023,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="10" t="s">
         <v>692</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14" t="s">
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10" t="s">
         <v>752</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14" t="s">
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="15"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11"/>
       <c r="I2" t="s">
         <v>750</v>
       </c>
@@ -12085,31 +12084,31 @@
       <c r="N2" t="s">
         <v>700</v>
       </c>
-      <c r="O2" s="14"/>
+      <c r="O2" s="10"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="13" t="s">
         <v>693</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="E3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="14">
         <v>302.39999999999998</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="15">
         <f>G3/207.9</f>
         <v>1.4545454545454544</v>
       </c>
@@ -12131,19 +12130,19 @@
       <c r="N3">
         <v>30</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
       <c r="I4" s="2" t="s">
         <v>549</v>
       </c>
@@ -12162,17 +12161,17 @@
       <c r="N4" s="7">
         <v>0.12</v>
       </c>
-      <c r="O4" s="11"/>
+      <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="12"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15"/>
       <c r="I5" s="2" t="s">
         <v>560</v>
       </c>
@@ -12191,17 +12190,17 @@
       <c r="N5" s="8">
         <v>0.1</v>
       </c>
-      <c r="O5" s="11"/>
+      <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="12"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="15"/>
       <c r="I6" s="2" t="s">
         <v>550</v>
       </c>
@@ -12220,31 +12219,31 @@
       <c r="N6" s="7">
         <v>0.2</v>
       </c>
-      <c r="O6" s="11"/>
+      <c r="O6" s="12"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="13" t="s">
         <v>694</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="E7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="14">
         <v>123</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="15">
         <f>G7/84.15</f>
         <v>1.4616755793226381</v>
       </c>
@@ -12266,19 +12265,19 @@
       <c r="N7" s="7">
         <v>0.3</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="12"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15"/>
       <c r="I8" s="2" t="s">
         <v>552</v>
       </c>
@@ -12297,17 +12296,17 @@
       <c r="N8" s="7">
         <v>0.12</v>
       </c>
-      <c r="O8" s="11"/>
+      <c r="O8" s="12"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="15"/>
       <c r="I9" s="2" t="s">
         <v>560</v>
       </c>
@@ -12326,17 +12325,17 @@
       <c r="N9" s="8">
         <v>0.1</v>
       </c>
-      <c r="O9" s="11"/>
+      <c r="O9" s="12"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="12"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="15"/>
       <c r="I10" s="2" t="s">
         <v>553</v>
       </c>
@@ -12355,17 +12354,17 @@
       <c r="N10" s="7">
         <v>0.2</v>
       </c>
-      <c r="O10" s="11"/>
+      <c r="O10" s="12"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="12"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="15"/>
       <c r="I11" s="2" t="s">
         <v>554</v>
       </c>
@@ -12384,31 +12383,31 @@
       <c r="N11" s="7">
         <v>0.15</v>
       </c>
-      <c r="O11" s="11"/>
+      <c r="O11" s="12"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="13" t="s">
         <v>555</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="13" t="s">
         <v>695</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="13">
+      <c r="E12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="14">
         <v>122.4</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="15">
         <f>G12/84.15</f>
         <v>1.4545454545454546</v>
       </c>
@@ -12430,19 +12429,19 @@
       <c r="N12" s="7">
         <v>0.1</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="12" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="12"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15"/>
       <c r="I13" t="s">
         <v>557</v>
       </c>
@@ -12461,17 +12460,17 @@
       <c r="N13" s="7">
         <v>0.1</v>
       </c>
-      <c r="O13" s="11"/>
+      <c r="O13" s="12"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="12"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15"/>
       <c r="I14" t="s">
         <v>591</v>
       </c>
@@ -12490,17 +12489,17 @@
       <c r="N14" s="7">
         <v>0.1</v>
       </c>
-      <c r="O14" s="11"/>
+      <c r="O14" s="12"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="12"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15"/>
       <c r="I15" s="2" t="s">
         <v>558</v>
       </c>
@@ -12519,31 +12518,31 @@
       <c r="N15" s="7">
         <v>0.2</v>
       </c>
-      <c r="O15" s="11"/>
+      <c r="O15" s="12"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="13" t="s">
         <v>696</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="E16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="14">
         <v>172.8</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="15">
         <f>G16/118.8</f>
         <v>1.4545454545454546</v>
       </c>
@@ -12565,19 +12564,19 @@
       <c r="N16" s="7">
         <v>0.3</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="12" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="12"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15"/>
       <c r="I17" s="2" t="s">
         <v>549</v>
       </c>
@@ -12596,17 +12595,17 @@
       <c r="N17" s="7">
         <v>0.12</v>
       </c>
-      <c r="O17" s="11"/>
+      <c r="O17" s="12"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="12"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
       <c r="I18" s="2" t="s">
         <v>560</v>
       </c>
@@ -12625,17 +12624,17 @@
       <c r="N18" s="8">
         <v>0.1</v>
       </c>
-      <c r="O18" s="11"/>
+      <c r="O18" s="12"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="12"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="15"/>
       <c r="I19" s="2" t="s">
         <v>562</v>
       </c>
@@ -12654,17 +12653,17 @@
       <c r="N19">
         <v>12</v>
       </c>
-      <c r="O19" s="11"/>
+      <c r="O19" s="12"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="12"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="15"/>
       <c r="I20" s="2" t="s">
         <v>561</v>
       </c>
@@ -12683,31 +12682,31 @@
       <c r="N20" s="7">
         <v>0.15</v>
       </c>
-      <c r="O20" s="11"/>
+      <c r="O20" s="12"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="13" t="s">
         <v>579</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="13" t="s">
         <v>696</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="13">
+      <c r="E21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="14">
         <v>230.4</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="15">
         <f>G21/158.4</f>
         <v>1.4545454545454546</v>
       </c>
@@ -12729,19 +12728,19 @@
       <c r="N21">
         <v>40</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="12" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="12"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="2" t="s">
         <v>565</v>
       </c>
@@ -12760,17 +12759,17 @@
       <c r="N22" s="7">
         <v>0.12</v>
       </c>
-      <c r="O22" s="11"/>
+      <c r="O22" s="12"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="12"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="15"/>
       <c r="I23" s="2" t="s">
         <v>566</v>
       </c>
@@ -12789,31 +12788,31 @@
       <c r="N23" s="8">
         <v>0.1</v>
       </c>
-      <c r="O23" s="11"/>
+      <c r="O23" s="12"/>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="13" t="s">
         <v>579</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="13" t="s">
         <v>693</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="13">
+      <c r="E24" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="14">
         <v>403.2</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="15">
         <f>G24/277.2</f>
         <v>1.4545454545454546</v>
       </c>
@@ -12835,19 +12834,19 @@
       <c r="N24">
         <v>40</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="12" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="12"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="15"/>
       <c r="I25" s="2" t="s">
         <v>549</v>
       </c>
@@ -12866,17 +12865,17 @@
       <c r="N25" s="7">
         <v>0.12</v>
       </c>
-      <c r="O25" s="11"/>
+      <c r="O25" s="12"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="12"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="15"/>
       <c r="I26" s="2" t="s">
         <v>560</v>
       </c>
@@ -12895,31 +12894,31 @@
       <c r="N26" s="8">
         <v>0.1</v>
       </c>
-      <c r="O26" s="11"/>
+      <c r="O26" s="12"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="13" t="s">
         <v>693</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="13">
+      <c r="E27" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="14">
         <v>302.39999999999998</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="15">
         <f>G27/207.9</f>
         <v>1.4545454545454544</v>
       </c>
@@ -12941,19 +12940,19 @@
       <c r="N27" s="7">
         <v>0.75</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="12" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="12"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="15"/>
       <c r="I28" s="2" t="s">
         <v>565</v>
       </c>
@@ -12972,17 +12971,17 @@
       <c r="N28" s="7">
         <v>0.12</v>
       </c>
-      <c r="O28" s="11"/>
+      <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="12"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="15"/>
       <c r="I29" s="2" t="s">
         <v>566</v>
       </c>
@@ -13001,17 +13000,17 @@
       <c r="N29" s="8">
         <v>0.1</v>
       </c>
-      <c r="O29" s="11"/>
+      <c r="O29" s="12"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="12"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
         <v>569</v>
       </c>
@@ -13030,17 +13029,17 @@
       <c r="N30" s="7">
         <v>0.2</v>
       </c>
-      <c r="O30" s="11"/>
+      <c r="O30" s="12"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="12"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="15"/>
       <c r="I31" s="2" t="s">
         <v>570</v>
       </c>
@@ -13059,31 +13058,31 @@
       <c r="N31" s="7">
         <v>1</v>
       </c>
-      <c r="O31" s="11"/>
+      <c r="O31" s="12"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="13" t="s">
         <v>697</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="14">
         <v>360</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="14">
         <v>240</v>
       </c>
-      <c r="G32" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" s="12">
+      <c r="G32" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="15">
         <f>E32/247.5</f>
         <v>1.4545454545454546</v>
       </c>
@@ -13105,19 +13104,19 @@
       <c r="N32">
         <v>10</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="O32" s="12" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="12"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="15"/>
       <c r="I33" t="s">
         <v>572</v>
       </c>
@@ -13136,17 +13135,17 @@
       <c r="N33">
         <v>20</v>
       </c>
-      <c r="O33" s="11"/>
+      <c r="O33" s="12"/>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="12"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="15"/>
       <c r="I34" t="s">
         <v>573</v>
       </c>
@@ -13165,17 +13164,17 @@
       <c r="N34">
         <v>20</v>
       </c>
-      <c r="O34" s="11"/>
+      <c r="O34" s="12"/>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="12"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="15"/>
       <c r="I35" s="2" t="s">
         <v>574</v>
       </c>
@@ -13194,17 +13193,17 @@
       <c r="N35" s="8">
         <v>0.15</v>
       </c>
-      <c r="O35" s="11"/>
+      <c r="O35" s="12"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="12"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="15"/>
       <c r="I36" s="2" t="s">
         <v>575</v>
       </c>
@@ -13223,20 +13222,66 @@
       <c r="N36" s="8">
         <v>0.15</v>
       </c>
-      <c r="O36" s="11"/>
+      <c r="O36" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D27:D31"/>
+    <mergeCell ref="D32:D36"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="D16:D20"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="O27:O31"/>
+    <mergeCell ref="O32:O36"/>
+    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="H32:H36"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="F27:F31"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="G32:G36"/>
+    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="E32:E36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="O21:O23"/>
+    <mergeCell ref="O24:O26"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="O12:O15"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="E16:E20"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="O16:O20"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="C16:C20"/>
     <mergeCell ref="O3:O6"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="B7:B11"/>
@@ -13253,62 +13298,16 @@
     <mergeCell ref="G3:G6"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C11"/>
-    <mergeCell ref="O12:O15"/>
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="B16:B20"/>
-    <mergeCell ref="E16:E20"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="O16:O20"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="H16:H20"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="G12:G15"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="C16:C20"/>
-    <mergeCell ref="O21:O23"/>
-    <mergeCell ref="O24:O26"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="O27:O31"/>
-    <mergeCell ref="O32:O36"/>
-    <mergeCell ref="H27:H31"/>
-    <mergeCell ref="H32:H36"/>
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="F27:F31"/>
-    <mergeCell ref="G27:G31"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="G32:G36"/>
-    <mergeCell ref="F32:F36"/>
-    <mergeCell ref="E32:E36"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D27:D31"/>
-    <mergeCell ref="D32:D36"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="D16:D20"/>
-    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
@@ -13338,43 +13337,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="11" t="s">
         <v>611</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="17" t="s">
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="16" t="s">
         <v>671</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="14" t="s">
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
       <c r="G2" t="s">
         <v>750</v>
       </c>
@@ -13399,23 +13398,23 @@
       <c r="N2" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="O2" s="14"/>
+      <c r="O2" s="10"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>460</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="14">
         <v>192</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="15">
         <f>E3/132</f>
         <v>1.4545454545454546</v>
       </c>
@@ -13443,17 +13442,17 @@
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="12"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="15"/>
       <c r="G4" t="s">
         <v>613</v>
       </c>
@@ -13475,15 +13474,15 @@
       <c r="N4">
         <v>6</v>
       </c>
-      <c r="O4" s="11"/>
+      <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="12"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
       <c r="G5" t="s">
         <v>614</v>
       </c>
@@ -13508,23 +13507,23 @@
       <c r="N5">
         <v>20</v>
       </c>
-      <c r="O5" s="11"/>
+      <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="13"/>
+      <c r="D6" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <v>240</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <f>E6/165</f>
         <v>1.4545454545454546</v>
       </c>
@@ -13552,17 +13551,17 @@
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="12"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
       <c r="G7" t="s">
         <v>616</v>
       </c>
@@ -13587,15 +13586,15 @@
       <c r="N7">
         <v>20</v>
       </c>
-      <c r="O7" s="11"/>
+      <c r="O7" s="12"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="12"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15"/>
       <c r="G8" t="s">
         <v>617</v>
       </c>
@@ -13620,23 +13619,23 @@
       <c r="N8">
         <v>20</v>
       </c>
-      <c r="O8" s="11"/>
+      <c r="O8" s="12"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>541</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>240</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="15">
         <f>E9/165</f>
         <v>1.4545454545454546</v>
       </c>
@@ -13664,17 +13663,17 @@
       <c r="N9">
         <v>1</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="12"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15"/>
       <c r="G10" t="s">
         <v>616</v>
       </c>
@@ -13699,15 +13698,15 @@
       <c r="N10">
         <v>20</v>
       </c>
-      <c r="O10" s="11"/>
+      <c r="O10" s="12"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="12"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15"/>
       <c r="G11" t="s">
         <v>617</v>
       </c>
@@ -13732,23 +13731,23 @@
       <c r="N11">
         <v>20</v>
       </c>
-      <c r="O11" s="11"/>
+      <c r="O11" s="12"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13" t="s">
         <v>639</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <v>192</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="15">
         <f>E12/132</f>
         <v>1.4545454545454546</v>
       </c>
@@ -13776,17 +13775,17 @@
       <c r="N12">
         <v>1</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="12" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="12"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="15"/>
       <c r="G13" t="s">
         <v>619</v>
       </c>
@@ -13808,15 +13807,15 @@
       <c r="N13">
         <v>10</v>
       </c>
-      <c r="O13" s="11"/>
+      <c r="O13" s="12"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="12"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
       <c r="G14" t="s">
         <v>614</v>
       </c>
@@ -13841,23 +13840,23 @@
       <c r="N14">
         <v>20</v>
       </c>
-      <c r="O14" s="11"/>
+      <c r="O14" s="12"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="s">
         <v>636</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="14">
         <v>240</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="15">
         <f>E15/165</f>
         <v>1.4545454545454546</v>
       </c>
@@ -13885,17 +13884,17 @@
       <c r="N15">
         <v>1</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="12" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="12"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
       <c r="G16" t="s">
         <v>619</v>
       </c>
@@ -13917,15 +13916,15 @@
       <c r="N16">
         <v>10</v>
       </c>
-      <c r="O16" s="11"/>
+      <c r="O16" s="12"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="12"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="15"/>
       <c r="G17" t="s">
         <v>617</v>
       </c>
@@ -13950,23 +13949,23 @@
       <c r="N17">
         <v>20</v>
       </c>
-      <c r="O17" s="11"/>
+      <c r="O17" s="12"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>541</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13" t="s">
         <v>638</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="14">
         <v>192</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="15">
         <f>E18/132</f>
         <v>1.4545454545454546</v>
       </c>
@@ -13994,17 +13993,17 @@
       <c r="N18">
         <v>1</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="12" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="10"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="12"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="15"/>
       <c r="G19" t="s">
         <v>622</v>
       </c>
@@ -14026,15 +14025,15 @@
       <c r="N19">
         <v>6</v>
       </c>
-      <c r="O19" s="11"/>
+      <c r="O19" s="12"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="10"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="12"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="15"/>
       <c r="G20" t="s">
         <v>623</v>
       </c>
@@ -14059,23 +14058,23 @@
       <c r="N20">
         <v>20</v>
       </c>
-      <c r="O20" s="11"/>
+      <c r="O20" s="12"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="13"/>
+      <c r="D21" s="13" t="s">
         <v>639</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="14">
         <v>192</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="15">
         <f>E21/132</f>
         <v>1.4545454545454546</v>
       </c>
@@ -14103,17 +14102,17 @@
       <c r="N21">
         <v>1</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="12" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="12"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
       <c r="G22" t="s">
         <v>623</v>
       </c>
@@ -14138,15 +14137,15 @@
       <c r="N22">
         <v>20</v>
       </c>
-      <c r="O22" s="11"/>
+      <c r="O22" s="12"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="12"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="15"/>
       <c r="G23" t="s">
         <v>614</v>
       </c>
@@ -14171,23 +14170,23 @@
       <c r="N23">
         <v>20</v>
       </c>
-      <c r="O23" s="11"/>
+      <c r="O23" s="12"/>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="13" t="s">
         <v>464</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="14">
         <v>247</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="15">
         <f>E24/165</f>
         <v>1.4969696969696971</v>
       </c>
@@ -14215,17 +14214,17 @@
       <c r="N24">
         <v>1</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="12" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="12"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15"/>
       <c r="G25" t="s">
         <v>616</v>
       </c>
@@ -14250,15 +14249,15 @@
       <c r="N25">
         <v>20</v>
       </c>
-      <c r="O25" s="11"/>
+      <c r="O25" s="12"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="12"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="15"/>
       <c r="G26" t="s">
         <v>617</v>
       </c>
@@ -14283,23 +14282,23 @@
       <c r="N26">
         <v>20</v>
       </c>
-      <c r="O26" s="11"/>
+      <c r="O26" s="12"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="13" t="s">
         <v>505</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="17" t="s">
         <v>541</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10" t="s">
+      <c r="C27" s="13"/>
+      <c r="D27" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="14">
         <v>247</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="15">
         <f>E27/165</f>
         <v>1.4969696969696971</v>
       </c>
@@ -14327,17 +14326,17 @@
       <c r="N27">
         <v>1</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="12" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="10"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="12"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="15"/>
       <c r="G28" t="s">
         <v>622</v>
       </c>
@@ -14359,15 +14358,15 @@
       <c r="N28">
         <v>6</v>
       </c>
-      <c r="O28" s="11"/>
+      <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="10"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="12"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="15"/>
       <c r="G29" t="s">
         <v>627</v>
       </c>
@@ -14392,23 +14391,23 @@
       <c r="N29">
         <v>20</v>
       </c>
-      <c r="O29" s="11"/>
+      <c r="O29" s="12"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="17" t="s">
         <v>541</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10" t="s">
+      <c r="C30" s="13"/>
+      <c r="D30" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="14">
         <v>240</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="15">
         <f>E30/165</f>
         <v>1.4545454545454546</v>
       </c>
@@ -14436,17 +14435,17 @@
       <c r="N30">
         <v>1</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="O30" s="12" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="12"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="15"/>
       <c r="G31" t="s">
         <v>616</v>
       </c>
@@ -14471,15 +14470,15 @@
       <c r="N31">
         <v>20</v>
       </c>
-      <c r="O31" s="11"/>
+      <c r="O31" s="12"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="10"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="12"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="15"/>
       <c r="G32" t="s">
         <v>629</v>
       </c>
@@ -14492,23 +14491,23 @@
       <c r="J32" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="O32" s="11"/>
+      <c r="O32" s="12"/>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="13" t="s">
         <v>511</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13" t="s">
         <v>638</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="14">
         <v>192</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="15">
         <f>E33/132</f>
         <v>1.4545454545454546</v>
       </c>
@@ -14536,17 +14535,17 @@
       <c r="N33">
         <v>1</v>
       </c>
-      <c r="O33" s="11" t="s">
+      <c r="O33" s="12" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="12"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="15"/>
       <c r="G34" t="s">
         <v>623</v>
       </c>
@@ -14571,15 +14570,15 @@
       <c r="N34">
         <v>20</v>
       </c>
-      <c r="O34" s="11"/>
+      <c r="O34" s="12"/>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="12"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="15"/>
       <c r="G35" t="s">
         <v>614</v>
       </c>
@@ -14604,23 +14603,23 @@
       <c r="N35">
         <v>20</v>
       </c>
-      <c r="O35" s="11"/>
+      <c r="O35" s="12"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="13" t="s">
         <v>514</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="17" t="s">
         <v>541</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10" t="s">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="14">
         <v>144</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="15">
         <f>E36/99</f>
         <v>1.4545454545454546</v>
       </c>
@@ -14648,17 +14647,17 @@
       <c r="N36">
         <v>1</v>
       </c>
-      <c r="O36" s="11" t="s">
+      <c r="O36" s="12" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="10"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="12"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="15"/>
       <c r="G37" t="s">
         <v>632</v>
       </c>
@@ -14683,15 +14682,15 @@
       <c r="N37">
         <v>20</v>
       </c>
-      <c r="O37" s="11"/>
+      <c r="O37" s="12"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="10"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="12"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
       <c r="G38" t="s">
         <v>633</v>
       </c>
@@ -14716,10 +14715,86 @@
       <c r="N38">
         <v>20</v>
       </c>
-      <c r="O38" s="11"/>
+      <c r="O38" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="92">
+    <mergeCell ref="O36:O38"/>
+    <mergeCell ref="O18:O20"/>
+    <mergeCell ref="O21:O23"/>
+    <mergeCell ref="O24:O26"/>
+    <mergeCell ref="O27:O29"/>
+    <mergeCell ref="O30:O32"/>
+    <mergeCell ref="O33:O35"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="O12:O14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="O15:O17"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="J1:N1"/>
@@ -14736,82 +14811,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="O12:O14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="O15:O17"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="F33:F35"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="O36:O38"/>
-    <mergeCell ref="O18:O20"/>
-    <mergeCell ref="O21:O23"/>
-    <mergeCell ref="O24:O26"/>
-    <mergeCell ref="O27:O29"/>
-    <mergeCell ref="O30:O32"/>
-    <mergeCell ref="O33:O35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
@@ -15337,14 +15336,14 @@
       <c r="A1" t="s">
         <v>753</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="10" t="s">
         <v>754</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" cm="1">
